--- a/data/trans_orig/P05A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>531826</t>
+          <t>531643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>573498</t>
+          <t>573753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>516810</t>
+          <t>516048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>556202</t>
+          <t>558125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1063857</t>
+          <t>1059769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1122474</t>
+          <t>1121050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105378</t>
+          <t>104176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108558</t>
+          <t>106496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146378</t>
+          <t>145804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221055</t>
+          <t>222291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279379</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750181</t>
+          <t>747736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800059</t>
+          <t>797654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>699642</t>
+          <t>702874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>758237</t>
+          <t>756843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1466212</t>
+          <t>1464895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1541782</t>
+          <t>1540841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137224</t>
+          <t>140176</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183773</t>
+          <t>186659</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161951</t>
+          <t>164739</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214441</t>
+          <t>214890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>313551</t>
+          <t>315602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>384244</t>
+          <t>386773</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62036</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>54872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89657</t>
+          <t>89019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497267</t>
+          <t>496633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>540828</t>
+          <t>541492</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>506629</t>
+          <t>501855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>547422</t>
+          <t>546882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1014022</t>
+          <t>1014484</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078811</t>
+          <t>1077496</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118228</t>
+          <t>117623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>160901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106982</t>
+          <t>107242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144985</t>
+          <t>146938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233172</t>
+          <t>234898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294766</t>
+          <t>293886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>43126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>34785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64618</t>
+          <t>62865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>685392</t>
+          <t>682776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>735243</t>
+          <t>734753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>681765</t>
+          <t>681573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>739807</t>
+          <t>741793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1384438</t>
+          <t>1382709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1460108</t>
+          <t>1462818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168313</t>
+          <t>168439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>216866</t>
+          <t>215697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211699</t>
+          <t>212785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263389</t>
+          <t>267155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391589</t>
+          <t>391115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>464457</t>
+          <t>465445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>50469</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72131</t>
+          <t>71163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106775</t>
+          <t>108677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107440</t>
+          <t>105603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149444</t>
+          <t>149399</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2514451</t>
+          <t>2509516</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2606516</t>
+          <t>2606784</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2456402</t>
+          <t>2455923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2556986</t>
+          <t>2556397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4996877</t>
+          <t>4998598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5135074</t>
+          <t>5138122</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>569288</t>
+          <t>568350</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>655375</t>
+          <t>659665</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>632750</t>
+          <t>632594</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>720408</t>
+          <t>724066</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1225227</t>
+          <t>1228724</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1355834</t>
+          <t>1357246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78417</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114871</t>
+          <t>115947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165081</t>
+          <t>164089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217956</t>
+          <t>216051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253691</t>
+          <t>253328</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>320738</t>
+          <t>316534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>631695</t>
+          <t>630504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>659250</t>
+          <t>659200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>591112</t>
+          <t>590507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>627248</t>
+          <t>627757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1231271</t>
+          <t>1231538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1276276</t>
+          <t>1281038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38832</t>
+          <t>39594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>67151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59096</t>
+          <t>58967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92222</t>
+          <t>95441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107916</t>
+          <t>105199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151545</t>
+          <t>151607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>841503</t>
+          <t>846413</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>889555</t>
+          <t>891251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>842262</t>
+          <t>844879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>891879</t>
+          <t>894683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705293</t>
+          <t>1705594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1770816</t>
+          <t>1772447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106078</t>
+          <t>103621</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151390</t>
+          <t>147786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106855</t>
+          <t>104909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150737</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>220063</t>
+          <t>220324</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>282723</t>
+          <t>282972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>36539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>65951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>627055</t>
+          <t>629595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>669907</t>
+          <t>670960</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>635460</t>
+          <t>634245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>677851</t>
+          <t>676571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1276821</t>
+          <t>1280402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1334122</t>
+          <t>1335767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75442</t>
+          <t>74293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>111756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>77176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113548</t>
+          <t>113020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>162287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216652</t>
+          <t>214367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>53108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>700019</t>
+          <t>701701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>756001</t>
+          <t>754566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>787778</t>
+          <t>786965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>842677</t>
+          <t>841663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1503456</t>
+          <t>1505502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1582297</t>
+          <t>1582628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141790</t>
+          <t>140561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189671</t>
+          <t>187920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151936</t>
+          <t>152736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200898</t>
+          <t>200015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304494</t>
+          <t>302851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375534</t>
+          <t>375676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67280</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44213</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73460</t>
+          <t>73486</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89951</t>
+          <t>89335</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130057</t>
+          <t>130765</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2849446</t>
+          <t>2846352</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2938008</t>
+          <t>2933474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2908589</t>
+          <t>2906474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3000181</t>
+          <t>2997835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5792135</t>
+          <t>5788594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5915748</t>
+          <t>5912702</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>393689</t>
+          <t>397776</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>477121</t>
+          <t>475595</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>430946</t>
+          <t>429179</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>515749</t>
+          <t>511808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>846267</t>
+          <t>846882</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>961138</t>
+          <t>959629</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>67542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>104909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>101019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147296</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180840</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240698</t>
+          <t>242839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>608974</t>
+          <t>607829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>636703</t>
+          <t>637522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>608928</t>
+          <t>607004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>634872</t>
+          <t>634997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1225896</t>
+          <t>1227442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1265596</t>
+          <t>1265990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49107</t>
+          <t>50954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48281</t>
+          <t>48669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56445</t>
+          <t>55005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89520</t>
+          <t>88918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23814</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891360</t>
+          <t>889895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>932449</t>
+          <t>930374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>905600</t>
+          <t>907384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>946033</t>
+          <t>947551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1811830</t>
+          <t>1808857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1869178</t>
+          <t>1867554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>74917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112998</t>
+          <t>113395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75240</t>
+          <t>75079</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113649</t>
+          <t>111743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>158994</t>
+          <t>160081</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>210206</t>
+          <t>210401</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25613</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>605963</t>
+          <t>608567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650468</t>
+          <t>650124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>610420</t>
+          <t>612466</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>655548</t>
+          <t>657162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1233785</t>
+          <t>1232565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1295731</t>
+          <t>1295554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80832</t>
+          <t>81854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121031</t>
+          <t>119739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94496</t>
+          <t>92458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134397</t>
+          <t>132872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186481</t>
+          <t>186237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243873</t>
+          <t>241909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,82 +6910,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>34282</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>23759</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>46571</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>59702</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>45500</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>77478</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>5,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>34282</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>47455</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>59702</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>45011</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>76302</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>782104</t>
+          <t>780130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>823818</t>
+          <t>822008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>832763</t>
+          <t>831833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>883159</t>
+          <t>883265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1627731</t>
+          <t>1629016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1692229</t>
+          <t>1693995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90393</t>
+          <t>91538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127531</t>
+          <t>130712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115057</t>
+          <t>115608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159909</t>
+          <t>160711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219293</t>
+          <t>217105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279046</t>
+          <t>279065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>35941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50356</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83739</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2928051</t>
+          <t>2930651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3006962</t>
+          <t>3006579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3005538</t>
+          <t>3001524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3088312</t>
+          <t>3085756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5958420</t>
+          <t>5953218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6071663</t>
+          <t>6070705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>300915</t>
+          <t>303176</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>374507</t>
+          <t>374638</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>339054</t>
+          <t>338626</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>417635</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>665675</t>
+          <t>661186</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>769525</t>
+          <t>764242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96501</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85805</t>
+          <t>87817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130708</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159478</t>
+          <t>158586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215459</t>
+          <t>216227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>592905</t>
+          <t>591831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>613684</t>
+          <t>614285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>679771</t>
+          <t>678880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>701780</t>
+          <t>700396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1279722</t>
+          <t>1279930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1309026</t>
+          <t>1309726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>39423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41443</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1085632</t>
+          <t>1085962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1152851</t>
+          <t>1152076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866839</t>
+          <t>866140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893829</t>
+          <t>894247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1967226</t>
+          <t>1967124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2048528</t>
+          <t>2048378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71556</t>
+          <t>71258</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42807</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66032</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67681</t>
+          <t>70880</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126799</t>
+          <t>126744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43520</t>
+          <t>43084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64284</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>616930</t>
+          <t>620712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>652820</t>
+          <t>653006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>824378</t>
+          <t>824395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>890664</t>
+          <t>897287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1463397</t>
+          <t>1461520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1545501</t>
+          <t>1543704</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79537</t>
+          <t>77847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33368</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91056</t>
+          <t>91937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80494</t>
+          <t>81556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151077</t>
+          <t>154486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>22482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>783748</t>
+          <t>782379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>832241</t>
+          <t>831177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>914944</t>
+          <t>915073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>971843</t>
+          <t>971573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1716192</t>
+          <t>1718547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1786749</t>
+          <t>1786562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107319</t>
+          <t>108995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93829</t>
+          <t>92621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139747</t>
+          <t>138883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173966</t>
+          <t>173088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232447</t>
+          <t>231740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46751</t>
+          <t>46632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49748</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88502</t>
+          <t>86347</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3123610</t>
+          <t>3126460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3234362</t>
+          <t>3235166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3331228</t>
+          <t>3323384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3436876</t>
+          <t>3429221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6478398</t>
+          <t>6472644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6622039</t>
+          <t>6617418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170623</t>
+          <t>163655</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>257336</t>
+          <t>254831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>210956</t>
+          <t>214342</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>295674</t>
+          <t>304770</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>418463</t>
+          <t>419031</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>535387</t>
+          <t>538389</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94070</t>
+          <t>96609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>121351</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172434</t>
+          <t>174157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>531643</t>
+          <t>532959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>573753</t>
+          <t>572568</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>516048</t>
+          <t>515747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>558125</t>
+          <t>558210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1059769</t>
+          <t>1060348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1121050</t>
+          <t>1120302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104176</t>
+          <t>106536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144795</t>
+          <t>146117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106496</t>
+          <t>105421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145804</t>
+          <t>146014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222291</t>
+          <t>224873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279964</t>
+          <t>279654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25385</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34303</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53279</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>747736</t>
+          <t>750113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>797654</t>
+          <t>799598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>702874</t>
+          <t>699875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>756843</t>
+          <t>758044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1464895</t>
+          <t>1470278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1540841</t>
+          <t>1543293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140176</t>
+          <t>138390</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186659</t>
+          <t>185033</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>163660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214890</t>
+          <t>215132</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>315602</t>
+          <t>313692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>386773</t>
+          <t>381843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34549</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63568</t>
+          <t>64531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54872</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89019</t>
+          <t>88900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>496633</t>
+          <t>497613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>541492</t>
+          <t>542543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>501855</t>
+          <t>504945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>546882</t>
+          <t>547009</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1014484</t>
+          <t>1015683</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077496</t>
+          <t>1081287</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117623</t>
+          <t>116791</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160901</t>
+          <t>160013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107242</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146938</t>
+          <t>147191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234898</t>
+          <t>234958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293886</t>
+          <t>295160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,42 +1891,42 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>29689</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20641</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42990</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>4,35%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29689</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20269</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43126</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34785</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62865</t>
+          <t>64014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>682776</t>
+          <t>684463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>734753</t>
+          <t>734585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>681573</t>
+          <t>682375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>741793</t>
+          <t>741366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1382709</t>
+          <t>1375561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1462818</t>
+          <t>1457994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168439</t>
+          <t>168283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215697</t>
+          <t>215458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212785</t>
+          <t>209319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>267155</t>
+          <t>262344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391115</t>
+          <t>392236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>465445</t>
+          <t>467599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>51869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>71850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108677</t>
+          <t>107520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105603</t>
+          <t>106441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149399</t>
+          <t>147782</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2509516</t>
+          <t>2511051</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2606784</t>
+          <t>2605799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2455923</t>
+          <t>2454741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2556397</t>
+          <t>2558527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4998598</t>
+          <t>4998356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5138122</t>
+          <t>5135256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>568350</t>
+          <t>569910</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>659665</t>
+          <t>659460</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>632594</t>
+          <t>632194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>724066</t>
+          <t>725107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1228724</t>
+          <t>1233066</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1357246</t>
+          <t>1353572</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77386</t>
+          <t>78243</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>115575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>163632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216051</t>
+          <t>220142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>253797</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316534</t>
+          <t>318891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>630504</t>
+          <t>630281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>659200</t>
+          <t>660236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>590507</t>
+          <t>591180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>627757</t>
+          <t>625507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1231538</t>
+          <t>1231626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1281038</t>
+          <t>1278293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>37953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>67216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58967</t>
+          <t>59944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>94030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105199</t>
+          <t>104951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151607</t>
+          <t>149588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>846413</t>
+          <t>844006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>891251</t>
+          <t>891047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>844879</t>
+          <t>842604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>894683</t>
+          <t>893534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705594</t>
+          <t>1705767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1772447</t>
+          <t>1772215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103621</t>
+          <t>107002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147786</t>
+          <t>152182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104909</t>
+          <t>105633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146823</t>
+          <t>149021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>220324</t>
+          <t>221471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>282972</t>
+          <t>285360</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>36518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>67905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>629595</t>
+          <t>627393</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>670960</t>
+          <t>670150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>634245</t>
+          <t>634808</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>676571</t>
+          <t>677309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1280402</t>
+          <t>1279317</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1335767</t>
+          <t>1336761</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>75649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111756</t>
+          <t>113955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77176</t>
+          <t>74880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113020</t>
+          <t>114543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162287</t>
+          <t>158193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214367</t>
+          <t>212551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,47 +4398,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14079</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>36382</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23078</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13817</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>36099</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>26286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>701701</t>
+          <t>700465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>754566</t>
+          <t>753403</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>786965</t>
+          <t>786093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>841663</t>
+          <t>842703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1505502</t>
+          <t>1505421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1582628</t>
+          <t>1583750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140561</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187920</t>
+          <t>188568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152736</t>
+          <t>152081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200015</t>
+          <t>201569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302851</t>
+          <t>304673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375676</t>
+          <t>375612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68325</t>
+          <t>68456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>74474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89335</t>
+          <t>92069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130765</t>
+          <t>133207</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2846352</t>
+          <t>2851544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2933474</t>
+          <t>2936555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2906474</t>
+          <t>2906297</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2997835</t>
+          <t>3000164</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5788594</t>
+          <t>5788928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5912702</t>
+          <t>5913425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>397776</t>
+          <t>400531</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>475595</t>
+          <t>473127</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>429179</t>
+          <t>427551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>511808</t>
+          <t>508731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>846882</t>
+          <t>845079</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959629</t>
+          <t>963012</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67542</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104909</t>
+          <t>108082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101019</t>
+          <t>102858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148553</t>
+          <t>149023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183156</t>
+          <t>182766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242839</t>
+          <t>239735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607829</t>
+          <t>607787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>637522</t>
+          <t>637934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>607004</t>
+          <t>608650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>634997</t>
+          <t>635202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1227442</t>
+          <t>1227485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1265990</t>
+          <t>1264986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25506</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55005</t>
+          <t>56433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88918</t>
+          <t>90742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889895</t>
+          <t>888158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>930374</t>
+          <t>930537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>907384</t>
+          <t>906292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>947551</t>
+          <t>947689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1808857</t>
+          <t>1809991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1867554</t>
+          <t>1868323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74917</t>
+          <t>75525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113395</t>
+          <t>114283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>73608</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111743</t>
+          <t>112414</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>160081</t>
+          <t>158241</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>210401</t>
+          <t>213096</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47377</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>608567</t>
+          <t>608622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650124</t>
+          <t>649070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>612466</t>
+          <t>610262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>655677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1232565</t>
+          <t>1234249</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1295554</t>
+          <t>1296784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>82563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119739</t>
+          <t>120269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92458</t>
+          <t>94420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132872</t>
+          <t>134201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186237</t>
+          <t>185888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241909</t>
+          <t>243109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46571</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45500</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>76720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>780130</t>
+          <t>779796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>822008</t>
+          <t>822169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>831833</t>
+          <t>832783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>883265</t>
+          <t>882234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1629016</t>
+          <t>1627135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1693995</t>
+          <t>1693232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91538</t>
+          <t>91562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130712</t>
+          <t>129297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115608</t>
+          <t>114675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160711</t>
+          <t>161738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217105</t>
+          <t>218566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279065</t>
+          <t>275336</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35941</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50559</t>
+          <t>50158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80920</t>
+          <t>82619</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2930651</t>
+          <t>2930855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3006579</t>
+          <t>3006807</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3001524</t>
+          <t>3002458</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3085756</t>
+          <t>3084034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5953218</t>
+          <t>5949200</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6070705</t>
+          <t>6068194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>303176</t>
+          <t>301875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>374638</t>
+          <t>372033</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>338626</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>417635</t>
+          <t>415241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,47 +7744,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>714186</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>663978</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>772298</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>9,6%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>714186</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>661186</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>764242</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64735</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101193</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87817</t>
+          <t>87966</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132957</t>
+          <t>130567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158586</t>
+          <t>161228</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216227</t>
+          <t>212767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>604404</t>
+          <t>657708</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>591831</t>
+          <t>643531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>614285</t>
+          <t>666422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>691889</t>
+          <t>697028</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>678880</t>
+          <t>685333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>700396</t>
+          <t>705997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1296293</t>
+          <t>1354737</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1279930</t>
+          <t>1336243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1309726</t>
+          <t>1367522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>27296</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>21559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>44649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68621</t>
+          <t>74523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -8490,22 +8490,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>633311</t>
+          <t>688438</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>633311</t>
+          <t>688438</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>633311</t>
+          <t>688438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1358642</t>
+          <t>1422618</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1358642</t>
+          <t>1422618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1358642</t>
+          <t>1422618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1115199</t>
+          <t>958894</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1085962</t>
+          <t>936400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1152076</t>
+          <t>977339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>882017</t>
+          <t>986546</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866140</t>
+          <t>971192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>894247</t>
+          <t>1001347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1997216</t>
+          <t>1945440</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1967124</t>
+          <t>1920520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2048378</t>
+          <t>1969685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>59023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>44254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71258</t>
+          <t>78077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53093</t>
+          <t>59929</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>48338</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66445</t>
+          <t>73651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>103558</t>
+          <t>118952</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>70880</t>
+          <t>98091</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126744</t>
+          <t>139035</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>47914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,17 +8981,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29377</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65631</t>
+          <t>71827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>955890</t>
+          <t>1069666</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>955890</t>
+          <t>1069666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>955890</t>
+          <t>1069666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2148754</t>
+          <t>2118583</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2148754</t>
+          <t>2118583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2148754</t>
+          <t>2118583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>638000</t>
+          <t>723145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>620712</t>
+          <t>703705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>653006</t>
+          <t>740870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>856459</t>
+          <t>723289</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>824395</t>
+          <t>703997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>897287</t>
+          <t>740261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1494458</t>
+          <t>1446434</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1461520</t>
+          <t>1416906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1543704</t>
+          <t>1470672</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45316</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63554</t>
+          <t>73746</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>58403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91937</t>
+          <t>93307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122973</t>
+          <t>143929</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81556</t>
+          <t>120125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154486</t>
+          <t>169636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>811416</t>
+          <t>869690</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>782379</t>
+          <t>844398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>831177</t>
+          <t>889141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>938981</t>
+          <t>935740</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>915073</t>
+          <t>914379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>971573</t>
+          <t>955257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1750398</t>
+          <t>1805431</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1718547</t>
+          <t>1771475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1786562</t>
+          <t>1832779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84144</t>
+          <t>89387</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66848</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108995</t>
+          <t>110334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>118397</t>
+          <t>142696</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92621</t>
+          <t>124201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138883</t>
+          <t>162625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>202542</t>
+          <t>232083</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173088</t>
+          <t>207561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231740</t>
+          <t>263910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>51716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>68594</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86347</t>
+          <t>87966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1093146</t>
+          <t>1117164</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1093146</t>
+          <t>1117164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1093146</t>
+          <t>1117164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019814</t>
+          <t>2106109</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019814</t>
+          <t>2106109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019814</t>
+          <t>2106109</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3169019</t>
+          <t>3209439</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3126460</t>
+          <t>3171024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3235166</t>
+          <t>3248306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3369346</t>
+          <t>3342604</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3323384</t>
+          <t>3308476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3429221</t>
+          <t>3377601</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6538366</t>
+          <t>6552042</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6472644</t>
+          <t>6500496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6617418</t>
+          <t>6602458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>219493</t>
+          <t>245889</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163655</t>
+          <t>211752</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>254831</t>
+          <t>279937</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>262448</t>
+          <t>306385</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>214342</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>304770</t>
+          <t>339284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>481941</t>
+          <t>552274</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>419031</t>
+          <t>508182</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>538389</t>
+          <t>601828</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68846</t>
+          <t>72867</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>55230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92096</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>75938</t>
+          <t>84280</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59914</t>
+          <t>68824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96609</t>
+          <t>103361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>144785</t>
+          <t>157147</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121351</t>
+          <t>133461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174157</t>
+          <t>182330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3457358</t>
+          <t>3528195</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3457358</t>
+          <t>3528195</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3457358</t>
+          <t>3528195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3707732</t>
+          <t>3733269</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3707732</t>
+          <t>3733269</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3707732</t>
+          <t>3733269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7165091</t>
+          <t>7261464</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7165091</t>
+          <t>7261464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7165091</t>
+          <t>7261464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
